--- a/2025-2026_Boards/FDCAN-USB_Board/Manufacturing/JLCPCB_FDCAN-USB_CPL.xlsx
+++ b/2025-2026_Boards/FDCAN-USB_Board/Manufacturing/JLCPCB_FDCAN-USB_CPL.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dawso\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dawso\Desktop\MarsRover\KiCad\2025-2026_Boards\FDCAN-USB_Board\Manufacturing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0791BFD0-BFE7-4393-BCA3-50180C3CC317}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA217E59-43E4-4540-AAAB-873412713D5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="135">
   <si>
     <t>Designator</t>
   </si>
@@ -149,9 +149,6 @@
     <t>J6</t>
   </si>
   <si>
-    <t>J7</t>
-  </si>
-  <si>
     <t>R1</t>
   </si>
   <si>
@@ -290,9 +287,6 @@
     <t>88.25mm</t>
   </si>
   <si>
-    <t>111.25mm</t>
-  </si>
-  <si>
     <t>79.5mm</t>
   </si>
   <si>
@@ -413,9 +407,6 @@
     <t>-66.54375mm</t>
   </si>
   <si>
-    <t>-62.29375mm</t>
-  </si>
-  <si>
     <t>-73.25mm</t>
   </si>
   <si>
@@ -435,6 +426,18 @@
   </si>
   <si>
     <t>-60.5mm</t>
+  </si>
+  <si>
+    <t>111.75mm</t>
+  </si>
+  <si>
+    <t>-62.25mm</t>
+  </si>
+  <si>
+    <t>-70.75mm</t>
+  </si>
+  <si>
+    <t>J1</t>
   </si>
 </sst>
 </file>
@@ -547,13 +550,13 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -831,7 +834,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E151"/>
+  <dimension ref="A1:E138"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="13.5546875" customWidth="1"/>
@@ -863,10 +866,10 @@
         <v>5</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>6</v>
@@ -880,10 +883,10 @@
         <v>7</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>6</v>
@@ -897,10 +900,10 @@
         <v>8</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>6</v>
@@ -914,10 +917,10 @@
         <v>10</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>6</v>
@@ -931,10 +934,10 @@
         <v>11</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>6</v>
@@ -948,10 +951,10 @@
         <v>12</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>6</v>
@@ -965,10 +968,10 @@
         <v>13</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>6</v>
@@ -982,10 +985,10 @@
         <v>14</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>6</v>
@@ -999,10 +1002,10 @@
         <v>15</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>6</v>
@@ -1016,10 +1019,10 @@
         <v>16</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>6</v>
@@ -1033,10 +1036,10 @@
         <v>17</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>6</v>
@@ -1050,10 +1053,10 @@
         <v>18</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>6</v>
@@ -1067,10 +1070,10 @@
         <v>19</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>6</v>
@@ -1084,10 +1087,10 @@
         <v>20</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>6</v>
@@ -1101,10 +1104,10 @@
         <v>21</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>6</v>
@@ -1118,10 +1121,10 @@
         <v>22</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>6</v>
@@ -1135,10 +1138,10 @@
         <v>23</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>6</v>
@@ -1152,10 +1155,10 @@
         <v>24</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>6</v>
@@ -1169,10 +1172,10 @@
         <v>25</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>6</v>
@@ -1186,10 +1189,10 @@
         <v>26</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>6</v>
@@ -1203,10 +1206,10 @@
         <v>27</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>6</v>
@@ -1220,10 +1223,10 @@
         <v>28</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>6</v>
@@ -1237,10 +1240,10 @@
         <v>29</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>6</v>
@@ -1254,10 +1257,10 @@
         <v>30</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>6</v>
@@ -1271,10 +1274,10 @@
         <v>31</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>6</v>
@@ -1288,10 +1291,10 @@
         <v>32</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>6</v>
@@ -1302,30 +1305,30 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="2" t="s">
-        <v>33</v>
+        <v>134</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>122</v>
+        <v>84</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>109</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>6</v>
       </c>
       <c r="E28" s="2">
-        <v>0</v>
+        <v>270</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>6</v>
@@ -1336,13 +1339,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>6</v>
@@ -1353,64 +1356,64 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>6</v>
       </c>
       <c r="E31" s="2">
-        <v>180</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>78</v>
+        <v>131</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>6</v>
       </c>
       <c r="E32" s="2">
-        <v>180</v>
+        <v>90</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>111</v>
+        <v>122</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>6</v>
       </c>
       <c r="E33" s="2">
-        <v>270</v>
+        <v>90</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>6</v>
@@ -1424,27 +1427,27 @@
         <v>9</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>6</v>
       </c>
       <c r="E35" s="2">
-        <v>270</v>
+        <v>90</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>6</v>
@@ -1455,13 +1458,13 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>6</v>
@@ -1472,13 +1475,13 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>6</v>
@@ -1489,13 +1492,13 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>6</v>
@@ -1506,13 +1509,13 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>6</v>
@@ -1523,13 +1526,13 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>6</v>
@@ -1540,13 +1543,13 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>6</v>
@@ -1557,13 +1560,13 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>6</v>
@@ -1574,13 +1577,13 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>6</v>
@@ -1591,13 +1594,13 @@
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>6</v>
@@ -1608,13 +1611,13 @@
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>6</v>
@@ -1625,13 +1628,13 @@
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>6</v>
@@ -1642,13 +1645,13 @@
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>6</v>
@@ -1659,13 +1662,13 @@
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>106</v>
+        <v>133</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>6</v>
@@ -1676,13 +1679,13 @@
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>6</v>
@@ -1693,13 +1696,13 @@
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>6</v>
@@ -1710,13 +1713,13 @@
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>6</v>
@@ -1727,13 +1730,13 @@
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>6</v>
@@ -1744,13 +1747,13 @@
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>6</v>
@@ -1760,7 +1763,7 @@
       </c>
     </row>
     <row r="55" spans="1:5">
-      <c r="A55" s="6"/>
+      <c r="A55" s="5"/>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="4"/>
@@ -2010,45 +2013,6 @@
     </row>
     <row r="138" spans="1:1">
       <c r="A138" s="4"/>
-    </row>
-    <row r="139" spans="1:1">
-      <c r="A139" s="5"/>
-    </row>
-    <row r="140" spans="1:1">
-      <c r="A140" s="5"/>
-    </row>
-    <row r="141" spans="1:1">
-      <c r="A141" s="5"/>
-    </row>
-    <row r="142" spans="1:1">
-      <c r="A142" s="5"/>
-    </row>
-    <row r="143" spans="1:1">
-      <c r="A143" s="5"/>
-    </row>
-    <row r="144" spans="1:1">
-      <c r="A144" s="5"/>
-    </row>
-    <row r="145" spans="1:1">
-      <c r="A145" s="5"/>
-    </row>
-    <row r="146" spans="1:1">
-      <c r="A146" s="5"/>
-    </row>
-    <row r="147" spans="1:1">
-      <c r="A147" s="5"/>
-    </row>
-    <row r="148" spans="1:1">
-      <c r="A148" s="5"/>
-    </row>
-    <row r="149" spans="1:1">
-      <c r="A149" s="5"/>
-    </row>
-    <row r="150" spans="1:1">
-      <c r="A150" s="5"/>
-    </row>
-    <row r="151" spans="1:1">
-      <c r="A151" s="5"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
